--- a/Result/profitability/3168.xlsx
+++ b/Result/profitability/3168.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM45"/>
+  <dimension ref="A1:AM46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.55</v>
       </c>
       <c r="M2" t="n">
-        <v>0.64</v>
+        <v>0.64875</v>
       </c>
       <c r="N2" t="n">
-        <v>23.31375</v>
+        <v>23.08125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4175</v>
+        <v>0.44375</v>
       </c>
       <c r="N3" t="n">
-        <v>21.3425</v>
+        <v>21.06125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.97</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09375</v>
+        <v>0.1275</v>
       </c>
       <c r="N4" t="n">
-        <v>17.7325</v>
+        <v>17.42625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.59</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04999999999999999</v>
+        <v>-0.02125</v>
       </c>
       <c r="N5" t="n">
-        <v>16.01625</v>
+        <v>15.795</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07499999999999998</v>
+        <v>-0.06875000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>14.87625</v>
+        <v>14.71875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.22</v>
+        <v>-0.1975</v>
       </c>
       <c r="N7" t="n">
-        <v>13.26625</v>
+        <v>13.00625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -6143,6 +6143,133 @@
       </c>
       <c r="AM45" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3168</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D46" t="n">
+        <v>785</v>
+      </c>
+      <c r="E46" t="n">
+        <v>235</v>
+      </c>
+      <c r="F46" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="G46" t="n">
+        <v>87</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>8.56%</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>-2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>85</v>
+      </c>
+      <c r="K46" t="n">
+        <v>62</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="N46" t="n">
+        <v>24.4875</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.3833333333333333</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0.01096010521701007</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0.3833333333333333</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>-0.07128473620620213</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
